--- a/Excel/SkillDoubleHitConfig.xlsx
+++ b/Excel/SkillDoubleHitConfig.xlsx
@@ -4,12 +4,25 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -73,28 +86,28 @@
     <t>string</t>
   </si>
   <si>
-    <t>连击·半月弯刀</t>
-  </si>
-  <si>
-    <t>释放攻击技能之后，15%概率追加一次半月弯刀</t>
-  </si>
-  <si>
-    <t>连击·爆裂火焰</t>
-  </si>
-  <si>
-    <t>释放攻击技能之后，15%概率追加一次爆裂火焰</t>
-  </si>
-  <si>
-    <t>连击·施毒术</t>
-  </si>
-  <si>
-    <t>释放攻击技能之后，15%概率追加一次施毒术</t>
+    <t>连击·旋风斩</t>
+  </si>
+  <si>
+    <t>释放攻击技能之后，15%概率追加一次旋风斩</t>
+  </si>
+  <si>
+    <t>连击·烈焰环</t>
+  </si>
+  <si>
+    <t>释放攻击技能之后，15%概率追加一次烈焰环</t>
+  </si>
+  <si>
+    <t>连击·毒咒术</t>
+  </si>
+  <si>
+    <t>释放攻击技能之后，15%概率追加一次毒咒术</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1199,7 +1212,7 @@
     <row r="37" s="1" customFormat="1"/>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3 D3 E3 F3 G3 F4 G4 F5 G5 E4:E5 C4:D5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:G3 F4:G4 F5:G5 C4:E5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
